--- a/artfynd/A 26992-2026 artfynd.xlsx
+++ b/artfynd/A 26992-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131598713</v>
+        <v>131598321</v>
       </c>
       <c r="B2" t="n">
-        <v>101260</v>
+        <v>99218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691139</v>
+        <v>691062</v>
       </c>
       <c r="R2" t="n">
-        <v>6379499</v>
+        <v>6379450</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>Handfull</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131598670</v>
+        <v>131597992</v>
       </c>
       <c r="B3" t="n">
-        <v>101260</v>
+        <v>110159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691116</v>
+        <v>691064</v>
       </c>
       <c r="R3" t="n">
-        <v>6379456</v>
+        <v>6379446</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tämligen riklig</t>
+          <t>Sparsam</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131597992</v>
+        <v>131598670</v>
       </c>
       <c r="B4" t="n">
-        <v>110012</v>
+        <v>101403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691064</v>
+        <v>691116</v>
       </c>
       <c r="R4" t="n">
-        <v>6379446</v>
+        <v>6379456</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sparsam</t>
+          <t>Tämligen riklig</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131598321</v>
+        <v>131598671</v>
       </c>
       <c r="B5" t="n">
-        <v>99077</v>
+        <v>101403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691062</v>
+        <v>691059</v>
       </c>
       <c r="R5" t="n">
-        <v>6379450</v>
+        <v>6379529</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Handfull</t>
+          <t>I kanten på hygge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,6 +1080,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131598713</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691139</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6379499</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26992-2026 artfynd.xlsx
+++ b/artfynd/A 26992-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131597992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598670</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>